--- a/Bonfiglioli/Motor Selection_Bonfiglioli.xlsx
+++ b/Bonfiglioli/Motor Selection_Bonfiglioli.xlsx
@@ -20,10 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
-  <si>
-    <t xml:space="preserve">"Humare application ke liye BMS better hai ya BMD+TQF combination? 
-Kya aap final recommendation de sakte hain?"</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
+  <si>
+    <t xml:space="preserve">Question</t>
   </si>
   <si>
     <t xml:space="preserve">Specification</t>
@@ -35,15 +34,19 @@
     <t xml:space="preserve">Motor - 2 (For joint 2, 3 &amp; 4)</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 1 ke liye 960 kg·m² reflected inertia hai - kya aapki recommendation isko handle kar sakti hai? 
-Inertia matching ratio kya hoga?”</t>
+    <t xml:space="preserve">Selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you provide final approval for the BMD + TQF with HB combination for Joint 1?</t>
   </si>
   <si>
     <t xml:space="preserve">Qunatity</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 1 ke liye 960 kg·m² reflected inertia hai - kya aapki recommendation isko handle kar sakti hai? 
-Inertia matching ratio kya hoga?"</t>
+    <t xml:space="preserve">Sizing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The reflected inertia for Joint 1 is 960 kg·m². Can this be handled, and is the F1 (additional inertia) option sufficient? What would be the inertia matching ratio?</t>
   </si>
   <si>
     <t xml:space="preserve">Rated Torque </t>
@@ -55,6 +58,9 @@
     <t xml:space="preserve">50 Nm</t>
   </si>
   <si>
+    <t xml:space="preserve">The peak radial load for Joint 1 is 9000 N. Can the TQF 160 with HB (reinforced bearings) reliably handle this load? What is the exact maximum radial load capacity?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peak Torque (Optional)</t>
   </si>
   <si>
@@ -64,7 +70,7 @@
     <t xml:space="preserve">170 Nm</t>
   </si>
   <si>
-    <t xml:space="preserve">"Kya aap AxiaVert drive ke liye ESD file de sakte hain for EtherCAT integration?"</t>
+    <t xml:space="preserve">For Joints 2, 3, and 4, is the BMS series the correct choice? Do any of these joints require up-sizing?</t>
   </si>
   <si>
     <t xml:space="preserve">Rated speed</t>
@@ -73,7 +79,10 @@
     <t xml:space="preserve">30 - 50 RPM</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 1 ke liye kaunsa motor model best rahega - BMD 170 ya BMD 145?"</t>
+    <t xml:space="preserve">Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you provide the ESD/ESI file for the AxiaVert drive for EtherCAT integration?</t>
   </si>
   <si>
     <t xml:space="preserve">Gear Type</t>
@@ -82,7 +91,7 @@
     <t xml:space="preserve">Precision Planetary Gear</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 2-4 ke liye BMD 118 14 Nm sahi rahega ya kuch aur?"</t>
+    <t xml:space="preserve">We have selected AXV 11K for Joint 1 and AXV 5K5 / 4K0 / 2K2 for Joints 2-4. Is this sizing correct?</t>
   </si>
   <si>
     <t xml:space="preserve">Gear Backlash</t>
@@ -91,7 +100,10 @@
     <t xml:space="preserve">Minimized</t>
   </si>
   <si>
-    <t xml:space="preserve">"Kya ENB11 (Hiperface DSL) encoder available hai? Iski resolution kya hai?"</t>
+    <t xml:space="preserve">Safety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We plan to use the S option (STO + SS1-t + SBC) for functional safety. Is this sufficient for a robotic application?</t>
   </si>
   <si>
     <t xml:space="preserve">Electromagnetic Brake</t>
@@ -100,7 +112,10 @@
     <t xml:space="preserve">Required</t>
   </si>
   <si>
-    <t xml:space="preserve">"Electromagnetic brake sabhi motors mein lagega? Brake torque kitna hai?"</t>
+    <t xml:space="preserve">Cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The cable length is 15 meters. Are there any derating or signal attenuation issues we should be aware of for power and signal cables?</t>
   </si>
   <si>
     <t xml:space="preserve">Encoder for Servo drive</t>
@@ -109,7 +124,10 @@
     <t xml:space="preserve">Absolute encoder (Preferably &gt;= 12 bits) </t>
   </si>
   <si>
-    <t xml:space="preserve">"IP65 protection standard hai ya extra lagega?"</t>
+    <t xml:space="preserve">Mechanical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can you provide 3D CAD models (STEP files) for mechanical integration?</t>
   </si>
   <si>
     <t xml:space="preserve">Mounting type </t>
@@ -118,13 +136,19 @@
     <t xml:space="preserve">Flange</t>
   </si>
   <si>
-    <t xml:space="preserve">"Kya KTY ya PT1000 thermal sensor standard hai?"</t>
+    <t xml:space="preserve">Brake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Is the F24 (electromagnetic brake) standard or optional? What is the brake torque rating?</t>
   </si>
   <si>
     <t xml:space="preserve">Output shaft type</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 1 ke liye TQF 160 kaun sa ratio best rahega - 40:1, 50:1 ya 70:1?"</t>
+    <t xml:space="preserve">Commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is the total cost estimate for all 8 units?</t>
   </si>
   <si>
     <t xml:space="preserve">Power Supply</t>
@@ -133,7 +157,7 @@
     <t xml:space="preserve">Three Phase</t>
   </si>
   <si>
-    <t xml:space="preserve">"Joint 2-4 ke liye TQF 090 sahi hai ya TQF 130 lena padega?"</t>
+    <t xml:space="preserve">What is the lead time? When can we expect delivery?</t>
   </si>
   <si>
     <t xml:space="preserve">Application</t>
@@ -142,7 +166,10 @@
     <t xml:space="preserve">For use in joints of a robotic manipulator prototype as shown in Figure 1.</t>
   </si>
   <si>
-    <t xml:space="preserve">"Backlash standard (5') enough hai ya reduced (3') lena chahiye?"</t>
+    <t xml:space="preserve">Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do you have a service center in India? Is onsite commissioning support available?</t>
   </si>
   <si>
     <t xml:space="preserve">Compatible Servo drive Required</t>
@@ -151,82 +178,34 @@
     <t xml:space="preserve">EtherCAT enabled drive with Position, Velocity and Torque control modes</t>
   </si>
   <si>
-    <t xml:space="preserve">"Torsional stiffness kitni hai? Kya ye high dynamics ke liye enough hai?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cable length</t>
   </si>
   <si>
     <t xml:space="preserve">15 m</t>
   </si>
   <si>
-    <t xml:space="preserve">"Gearbox ka efficiency kitna hai? 1-stage aur 2-stage mein kya difference hai?"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Joint 1 ke liye AXV 4 A S D 7K5 sahi rahega ya 9K2 lena padega?"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Joint 2-4 ke liye AXV 4 A S D 3K0 enough hai?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Details required from CSIR-CMERI</t>
   </si>
   <si>
-    <t xml:space="preserve">"Functional Safety - STO, SS1-t, SBC - humein kaunsa chahiye? M ya S?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Load inertia reflected at the G.B output shaft</t>
   </si>
   <si>
-    <t xml:space="preserve">"Cable length 15m hai - koi signal attenuation issue toh nahi hoga?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Axial load and radial load for G.B selection</t>
   </si>
   <si>
-    <t xml:space="preserve">"OPC-UA support hai? Hum IIoT/Industry 4.0 ke liye data lena chahte hain."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Kya PLC programming (IEC 61131-3) support hai? Hum custom logic likhna chahte hain."</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"BMS + Axiavert drive - kya ye plug-and-play hai? Ya kuch special configuration chahiye?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Documentation to be shared From Bonfiglioli</t>
   </si>
   <si>
-    <t xml:space="preserve">"Hum EtherCAT use karenge. Kya aapke paas ESD file ready hai?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Motor (BMD) + GB (TQF)</t>
   </si>
   <si>
-    <t xml:space="preserve">"Kya aap 3D CAD models (STEP files) de sakte hain for mechanical integration?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">Integrated One (BMS)</t>
   </si>
   <si>
-    <t xml:space="preserve">"BMS ka mounting type kya hai? Hum flange mounting chahte hain."</t>
-  </si>
-  <si>
     <t xml:space="preserve">Drive Axia VERT (Drive)</t>
   </si>
   <si>
-    <t xml:space="preserve">"2 + 6 = 8 units ka total cost kya hoga?"</t>
-  </si>
-  <si>
     <t xml:space="preserve">ESD file for EtherCAT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Lead time kya hai? Delivery kab tak milegi?"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Warranty period kya hai?"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"India mein service center hai? Onsite support milega?"</t>
   </si>
   <si>
     <t xml:space="preserve">Figure 1</t>
@@ -365,7 +344,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
+      <sz val="15"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -415,7 +394,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -467,13 +446,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA9D18E"/>
-        <bgColor rgb="FF99CCFF"/>
+        <bgColor rgb="FFB4C7DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4C7DC"/>
+        <bgColor rgb="FFA9D18E"/>
       </patternFill>
     </fill>
     <fill>
@@ -627,73 +612,81 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="22" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -709,19 +702,39 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -740,7 +753,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,7 +765,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -800,7 +817,7 @@
       <rgbColor rgb="FF996600"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFA9D18E"/>
+      <rgbColor rgb="FFB4C7DC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -822,7 +839,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFA9D18E"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCCCC"/>
@@ -858,9 +875,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>48600</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>250200</xdr:rowOff>
+      <xdr:colOff>47880</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>164520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -873,8 +890,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18058680" y="5686200"/>
-          <a:ext cx="5335560" cy="3627360"/>
+          <a:off x="15402600" y="4815000"/>
+          <a:ext cx="5334840" cy="3626640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -895,13 +912,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:X172"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="89.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="64.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="40.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="28.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="33.57"/>
@@ -909,432 +926,522 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="43.85"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="3" customFormat="true" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="M1" s="4"/>
+    </row>
+    <row r="2" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="J2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="7" t="n">
+      <c r="J2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L2" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="M2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>8</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" s="3" customFormat="true" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="J4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="J4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="K4" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="J5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="15"/>
-    </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2"/>
+      <c r="J5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="17"/>
+    </row>
+    <row r="6" s="3" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="J6" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-    </row>
-    <row r="7" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="J6" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="J7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2"/>
+      <c r="J7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="J8" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-    </row>
-    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2"/>
+      <c r="J8" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="J9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2"/>
+      <c r="J9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" s="3" customFormat="true" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="J10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="2"/>
+      <c r="J10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+    </row>
+    <row r="11" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>39</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="J11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2"/>
+      <c r="J11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="J12" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="J12" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+    </row>
+    <row r="13" s="3" customFormat="true" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>45</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="J13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="X13" s="22"/>
-    </row>
-    <row r="14" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2"/>
+      <c r="J13" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="X13" s="24"/>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="J14" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="J14" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="19.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="J15" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="K15" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-    </row>
-    <row r="16" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-    </row>
-    <row r="17" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="28" t="s">
+      <c r="A15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="J15" s="28" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="K15" s="29" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30"/>
+      <c r="J18" s="35" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26"/>
+      <c r="J19" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="29" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30"/>
+      <c r="J20" s="36" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30"/>
+    </row>
+    <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26"/>
+      <c r="J23" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="J24" s="30" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30"/>
+      <c r="J24" s="38" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26"/>
+      <c r="J25" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="J25" s="30" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30"/>
+      <c r="J26" s="38" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26"/>
+      <c r="J27" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="J26" s="30" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="30"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="30"/>
+      <c r="L34" s="39" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J27" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="L34" s="31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="30"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="26"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="30"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="26"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="30"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="26"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="30"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="30"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="26"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="30"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="26"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="30"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="26"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="30"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="26"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="30"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="26"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="30"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="26"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="30"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="26"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="30"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="26"/>
+    </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
